--- a/AAII_Financials/Quarterly/IKTSY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IKTSY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="92">
   <si>
     <t>IKTSY</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -656,61 +656,68 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -738,8 +745,14 @@
       <c r="K8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -767,8 +780,14 @@
       <c r="K9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -796,8 +815,14 @@
       <c r="K10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -809,8 +834,10 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -838,8 +865,14 @@
       <c r="K12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -867,8 +900,14 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -896,8 +935,14 @@
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -925,8 +970,14 @@
       <c r="K15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -935,8 +986,10 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -964,8 +1017,14 @@
       <c r="K17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -993,8 +1052,14 @@
       <c r="K18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1006,8 +1071,10 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1035,8 +1102,14 @@
       <c r="K20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1064,8 +1137,14 @@
       <c r="K21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1093,8 +1172,14 @@
       <c r="K22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1122,8 +1207,14 @@
       <c r="K23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1151,8 +1242,14 @@
       <c r="K24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1180,8 +1277,14 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1209,8 +1312,14 @@
       <c r="K26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1238,8 +1347,14 @@
       <c r="K27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1267,8 +1382,14 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1296,8 +1417,14 @@
       <c r="K29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1325,8 +1452,14 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1354,8 +1487,14 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1383,8 +1522,14 @@
       <c r="K32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1412,8 +1557,14 @@
       <c r="K33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1441,8 +1592,14 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1470,42 +1627,54 @@
       <c r="K35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1517,8 +1686,10 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1530,37 +1701,45 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>429400</v>
+      </c>
+      <c r="E41" s="3">
+        <v>459700</v>
+      </c>
+      <c r="F41" s="3">
         <v>449800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>449500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>381200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>365200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>304400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>296300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>387500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>358400</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1588,66 +1767,84 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>998200</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1068600</v>
+      </c>
+      <c r="F43" s="3">
         <v>1020600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1020000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>894000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>856500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>1000500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>974000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>856600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>792200</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>23800</v>
+      </c>
+      <c r="E44" s="3">
+        <v>25500</v>
+      </c>
+      <c r="F44" s="3">
         <v>23300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>23200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>21900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>21000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>22200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>21600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>20400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>18800</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -1675,37 +1872,49 @@
       <c r="K45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1451400</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1553800</v>
+      </c>
+      <c r="F46" s="3">
         <v>1493700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>1492700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>1365000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>1307700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1327100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1291900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1321500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1222200</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1733,66 +1942,84 @@
       <c r="K47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>867300</v>
+      </c>
+      <c r="E48" s="3">
+        <v>928600</v>
+      </c>
+      <c r="F48" s="3">
         <v>838000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>837500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>852900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>817100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>830000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>808000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>836700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>773800</v>
       </c>
     </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2090800</v>
+      </c>
+      <c r="E49" s="3">
+        <v>2238400</v>
+      </c>
+      <c r="F49" s="3">
         <v>2173100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>2171700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>2186700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>2094900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>2163300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>2106000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>2146300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>1984900</v>
       </c>
     </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1820,8 +2047,14 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1849,37 +2082,49 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>34100</v>
+      </c>
+      <c r="E52" s="3">
+        <v>36500</v>
+      </c>
+      <c r="F52" s="3">
         <v>27700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>27700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>37800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>36200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>32000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>31200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>35800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>33100</v>
       </c>
     </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1907,37 +2152,49 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4506100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>4824200</v>
+      </c>
+      <c r="F54" s="3">
         <v>4596200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>4593200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>4506400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>4317400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>4429000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>4311700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>4410300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>4078600</v>
       </c>
     </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1949,8 +2206,10 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1962,182 +2221,220 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>948500</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1015400</v>
+      </c>
+      <c r="F57" s="3">
         <v>882500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>881900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>260900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>249900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>866000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>843100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>207400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>191800</v>
       </c>
     </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>214600</v>
+      </c>
+      <c r="E58" s="3">
+        <v>229700</v>
+      </c>
+      <c r="F58" s="3">
         <v>147100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>147000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>213200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>204300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>469900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>457500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>401200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>371100</v>
       </c>
     </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>151600</v>
+      </c>
+      <c r="E59" s="3">
+        <v>162300</v>
+      </c>
+      <c r="F59" s="3">
         <v>147600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>147500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>387000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>370700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>94800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>92300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>397000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>367200</v>
       </c>
     </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1314600</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1407500</v>
+      </c>
+      <c r="F60" s="3">
         <v>1177200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1176500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1250200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>1197700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>1430800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1392900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1377200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1273600</v>
       </c>
     </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1215600</v>
+      </c>
+      <c r="E61" s="3">
+        <v>1301400</v>
+      </c>
+      <c r="F61" s="3">
         <v>1570000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>1569000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>1337800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>1281700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>1218900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>1186700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>1263600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>1168600</v>
       </c>
     </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>72900</v>
+      </c>
+      <c r="E62" s="3">
+        <v>78000</v>
+      </c>
+      <c r="F62" s="3">
         <v>52100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>52000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>75800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>72600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>61600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>60000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>51300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>47500</v>
       </c>
     </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2165,8 +2462,14 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2194,8 +2497,14 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2223,37 +2532,49 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2697100</v>
+      </c>
+      <c r="E66" s="3">
+        <v>2887500</v>
+      </c>
+      <c r="F66" s="3">
         <v>2886100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>2884300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>2774000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>2657600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>2821400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>2746700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>2822200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>2610000</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2265,8 +2586,10 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2294,8 +2617,14 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2323,8 +2652,14 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2352,8 +2687,14 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2381,37 +2722,49 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1669700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>1787600</v>
+      </c>
+      <c r="F72" s="3">
         <v>1523600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>1522600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>1517700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>1454000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>1378000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>1341500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>1284300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>1187700</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2439,8 +2792,14 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2468,8 +2827,14 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2497,37 +2862,49 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1755100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1879000</v>
+      </c>
+      <c r="F76" s="3">
         <v>1653800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>1652700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>1685700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>1615000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>1563100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>1521700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>1547100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>1430800</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2555,42 +2932,54 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -2618,8 +3007,14 @@
       <c r="K81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2631,37 +3026,45 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>48500</v>
+      </c>
+      <c r="E83" s="3">
+        <v>46400</v>
+      </c>
+      <c r="F83" s="3">
         <v>50800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>49400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>49900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>46200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>47000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>50800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>52100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>51900</v>
       </c>
     </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2689,8 +3092,14 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2718,8 +3127,14 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2747,8 +3162,14 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2776,8 +3197,14 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2805,37 +3232,49 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>265100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>283800</v>
+      </c>
+      <c r="F89" s="3">
         <v>109700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>109600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>240700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>230600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>99800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>97100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>236400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>218600</v>
       </c>
     </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2847,37 +3286,45 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-49700</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-53200</v>
+      </c>
+      <c r="F91" s="3">
         <v>-35100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-35100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-41700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-40000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-32700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-31800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-45400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-42000</v>
       </c>
     </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2905,8 +3352,14 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2934,37 +3387,49 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-46200</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-49500</v>
+      </c>
+      <c r="F94" s="3">
         <v>-43200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-43200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-51700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-49500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-40700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-39600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-82200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-76000</v>
       </c>
     </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2976,37 +3441,45 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>54300</v>
+      </c>
+      <c r="E96" s="3">
+        <v>58200</v>
+      </c>
+      <c r="F96" s="3">
         <v>75400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>75300</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>38800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>37200</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>73300</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>71400</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>33200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>30700</v>
       </c>
     </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3034,8 +3507,14 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3063,8 +3542,14 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3092,91 +3577,115 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-226000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-241900</v>
+      </c>
+      <c r="F100" s="3">
         <v>-26200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-26100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-138000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-132200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-101300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-98700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-102200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-94500</v>
       </c>
     </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="F101" s="3">
         <v>-11900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-11600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-4600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-4200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>7700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>8300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>7500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="F102" s="3">
         <v>35600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>35600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>40200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>38500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-54100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-52700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>47400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>43800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IKTSY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IKTSY_QTR_FIN.xlsx
@@ -1779,10 +1779,10 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>998200</v>
+        <v>922500</v>
       </c>
       <c r="E43" s="3">
-        <v>1068600</v>
+        <v>987700</v>
       </c>
       <c r="F43" s="3">
         <v>1020600</v>
@@ -2094,10 +2094,10 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>34100</v>
+        <v>43900</v>
       </c>
       <c r="E52" s="3">
-        <v>36500</v>
+        <v>47000</v>
       </c>
       <c r="F52" s="3">
         <v>27700</v>
@@ -2229,10 +2229,10 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>948500</v>
+        <v>279200</v>
       </c>
       <c r="E57" s="3">
-        <v>1015400</v>
+        <v>298900</v>
       </c>
       <c r="F57" s="3">
         <v>882500</v>
@@ -2299,10 +2299,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>151600</v>
+        <v>421600</v>
       </c>
       <c r="E59" s="3">
-        <v>162300</v>
+        <v>451400</v>
       </c>
       <c r="F59" s="3">
         <v>147600</v>
@@ -2404,10 +2404,10 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>72900</v>
+        <v>45300</v>
       </c>
       <c r="E62" s="3">
-        <v>78000</v>
+        <v>48500</v>
       </c>
       <c r="F62" s="3">
         <v>52100</v>

--- a/AAII_Financials/Quarterly/IKTSY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IKTSY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="92">
   <si>
     <t>IKTSY</t>
   </si>
@@ -656,68 +656,76 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -751,8 +759,14 @@
       <c r="M8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -786,8 +800,14 @@
       <c r="M9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -821,8 +841,14 @@
       <c r="M10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -836,8 +862,10 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -871,8 +899,14 @@
       <c r="M12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -906,8 +940,14 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -941,8 +981,14 @@
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -976,8 +1022,14 @@
       <c r="M15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -988,8 +1040,10 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1023,8 +1077,14 @@
       <c r="M17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1058,8 +1118,14 @@
       <c r="M18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1073,8 +1139,10 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1108,8 +1176,14 @@
       <c r="M20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1143,8 +1217,14 @@
       <c r="M21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1178,8 +1258,14 @@
       <c r="M22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1213,8 +1299,14 @@
       <c r="M23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1248,8 +1340,14 @@
       <c r="M24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1283,8 +1381,14 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1318,8 +1422,14 @@
       <c r="M26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1353,8 +1463,14 @@
       <c r="M27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1388,8 +1504,14 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1423,8 +1545,14 @@
       <c r="M29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1458,8 +1586,14 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1493,8 +1627,14 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1528,8 +1668,14 @@
       <c r="M32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1563,8 +1709,14 @@
       <c r="M33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1598,8 +1750,14 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1633,48 +1791,60 @@
       <c r="M35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1688,8 +1858,10 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1703,43 +1875,51 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>500500</v>
+      </c>
+      <c r="E41" s="3">
+        <v>472000</v>
+      </c>
+      <c r="F41" s="3">
         <v>429400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>459700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>449800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>449500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>381200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>365200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>304400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>296300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>387500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>358400</v>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1773,78 +1953,96 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1091000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1028800</v>
+      </c>
+      <c r="F43" s="3">
         <v>922500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>987700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>1020600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>1020000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>894000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>856500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>1000500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>974000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>856600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>792200</v>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>27300</v>
+      </c>
+      <c r="E44" s="3">
+        <v>25700</v>
+      </c>
+      <c r="F44" s="3">
         <v>23800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>25500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>23300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>23200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>21900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>21000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>22200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>21600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>20400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>18800</v>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -1878,43 +2076,55 @@
       <c r="M45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1618700</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1526500</v>
+      </c>
+      <c r="F46" s="3">
         <v>1451400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>1553800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>1493700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>1492700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1365000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1307700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1327100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1291900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1321500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>1222200</v>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1948,78 +2158,96 @@
       <c r="M47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>923000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>870400</v>
+      </c>
+      <c r="F48" s="3">
         <v>867300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>928600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>838000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>837500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>852900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>817100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>830000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>808000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>836700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>773800</v>
       </c>
     </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2156500</v>
+      </c>
+      <c r="E49" s="3">
+        <v>2033600</v>
+      </c>
+      <c r="F49" s="3">
         <v>2090800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>2238400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>2173100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>2171700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>2186700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>2094900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>2163300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>2106000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>2146300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>1984900</v>
       </c>
     </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2053,8 +2281,14 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2088,43 +2322,55 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>38900</v>
+      </c>
+      <c r="E52" s="3">
+        <v>36700</v>
+      </c>
+      <c r="F52" s="3">
         <v>43900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>47000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>27700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>27700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>37800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>36200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>32000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>31200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>35800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>33100</v>
       </c>
     </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2158,43 +2404,55 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4806000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>4532200</v>
+      </c>
+      <c r="F54" s="3">
         <v>4506100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>4824200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>4596200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>4593200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>4506400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>4317400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>4429000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>4311700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>4410300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>4078600</v>
       </c>
     </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2208,8 +2466,10 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2223,218 +2483,256 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>945300</v>
+      </c>
+      <c r="E57" s="3">
+        <v>891500</v>
+      </c>
+      <c r="F57" s="3">
         <v>279200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>298900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>882500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>881900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>260900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>249900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>866000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>843100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>207400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>191800</v>
       </c>
     </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>170800</v>
+      </c>
+      <c r="E58" s="3">
+        <v>161100</v>
+      </c>
+      <c r="F58" s="3">
         <v>214600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>229700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>147100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>147000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>213200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>204300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>469900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>457500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>401200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>371100</v>
       </c>
     </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>95900</v>
+      </c>
+      <c r="E59" s="3">
+        <v>90400</v>
+      </c>
+      <c r="F59" s="3">
         <v>421600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>451400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>147600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>147500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>387000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>370700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>94800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>92300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>397000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>367200</v>
       </c>
     </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1212100</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1143000</v>
+      </c>
+      <c r="F60" s="3">
         <v>1314600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1407500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1177200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>1176500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>1250200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1197700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1430800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1392900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>1377200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>1273600</v>
       </c>
     </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1810900</v>
+      </c>
+      <c r="E61" s="3">
+        <v>1707800</v>
+      </c>
+      <c r="F61" s="3">
         <v>1215600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>1301400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>1570000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>1569000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>1337800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>1281700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>1218900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>1186700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>1263600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>1168600</v>
       </c>
     </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>90100</v>
+      </c>
+      <c r="E62" s="3">
+        <v>85000</v>
+      </c>
+      <c r="F62" s="3">
         <v>45300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>48500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>52100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>52000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>75800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>72600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>61600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>60000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>51300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>47500</v>
       </c>
     </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2468,8 +2766,14 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2503,8 +2807,14 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2538,43 +2848,55 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3202200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>3019800</v>
+      </c>
+      <c r="F66" s="3">
         <v>2697100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>2887500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>2886100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>2884300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>2774000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>2657600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>2821400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>2746700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>2822200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>2610000</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2588,8 +2910,10 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2623,8 +2947,14 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2658,8 +2988,14 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2693,8 +3029,14 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2728,43 +3070,55 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1560500</v>
+      </c>
+      <c r="E72" s="3">
+        <v>1471600</v>
+      </c>
+      <c r="F72" s="3">
         <v>1669700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>1787600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>1523600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>1522600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>1517700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>1454000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>1378000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>1341500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>1284300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>1187700</v>
       </c>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2798,8 +3152,14 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2833,8 +3193,14 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2868,43 +3234,55 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1546100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1458000</v>
+      </c>
+      <c r="F76" s="3">
         <v>1755100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>1879000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>1653800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>1652700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>1685700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>1615000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>1563100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>1521700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>1547100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>1430800</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2938,48 +3316,60 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3013,8 +3403,14 @@
       <c r="M81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3028,43 +3424,51 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>44700</v>
+      </c>
+      <c r="E83" s="3">
+        <v>44700</v>
+      </c>
+      <c r="F83" s="3">
         <v>48500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>46400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>50800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>49400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>49900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>46200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>47000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>50800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>52100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>51900</v>
       </c>
     </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3098,8 +3502,14 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3133,8 +3543,14 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3168,8 +3584,14 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3203,8 +3625,14 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3238,43 +3666,55 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>98600</v>
+      </c>
+      <c r="E89" s="3">
+        <v>93000</v>
+      </c>
+      <c r="F89" s="3">
         <v>265100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>283800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>109700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>109600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>240700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>230600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>99800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>97100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>236400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>218600</v>
       </c>
     </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3288,43 +3728,51 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-42300</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-39900</v>
+      </c>
+      <c r="F91" s="3">
         <v>-49700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-53200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-35100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-35100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-41700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-40000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-32700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-31800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-45400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-42000</v>
       </c>
     </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3358,8 +3806,14 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3393,43 +3847,55 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-45800</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-43200</v>
+      </c>
+      <c r="F94" s="3">
         <v>-46200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-49500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-43200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-43200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-51700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-49500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-40700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-39600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-82200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-76000</v>
       </c>
     </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3443,43 +3909,51 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>111700</v>
+      </c>
+      <c r="E96" s="3">
+        <v>105400</v>
+      </c>
+      <c r="F96" s="3">
         <v>54300</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>58200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>75400</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>75300</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>38800</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>37200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>73300</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>71400</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>33200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>30700</v>
       </c>
     </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3513,8 +3987,14 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3548,8 +4028,14 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3583,109 +4069,133 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-23400</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-22100</v>
+      </c>
+      <c r="F100" s="3">
         <v>-226000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-241900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-26200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-26100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-138000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-132200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-101300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-98700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-102200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-94500</v>
       </c>
     </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="F101" s="3">
         <v>-10900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-10400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-11900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-11600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-4600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-4200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>7700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>8300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>7500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>17100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>16100</v>
+      </c>
+      <c r="F102" s="3">
         <v>-11500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-12300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>35600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>35600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>40200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>38500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-54100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-52700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>47400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>43800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IKTSY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IKTSY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="92">
   <si>
     <t>IKTSY</t>
   </si>
@@ -656,76 +656,83 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -765,8 +772,14 @@
       <c r="O8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -806,8 +819,14 @@
       <c r="O9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -847,8 +866,14 @@
       <c r="O10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -864,8 +889,10 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -905,8 +932,14 @@
       <c r="O12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -946,8 +979,14 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -987,8 +1026,14 @@
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1028,8 +1073,14 @@
       <c r="O15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1042,8 +1093,10 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1083,8 +1136,14 @@
       <c r="O17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1124,8 +1183,14 @@
       <c r="O18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1141,8 +1206,10 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1182,8 +1249,14 @@
       <c r="O20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1223,8 +1296,14 @@
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1264,8 +1343,14 @@
       <c r="O22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1305,8 +1390,14 @@
       <c r="O23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1346,8 +1437,14 @@
       <c r="O24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1387,8 +1484,14 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1428,8 +1531,14 @@
       <c r="O26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1469,8 +1578,14 @@
       <c r="O27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1510,8 +1625,14 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1551,8 +1672,14 @@
       <c r="O29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1592,8 +1719,14 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1633,8 +1766,14 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1674,8 +1813,14 @@
       <c r="O32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1715,8 +1860,14 @@
       <c r="O33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1756,8 +1907,14 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1797,54 +1954,66 @@
       <c r="O35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1860,8 +2029,10 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1877,49 +2048,57 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>443100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>442500</v>
+      </c>
+      <c r="F41" s="3">
         <v>500500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>472000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>429400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>459700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>449800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>449500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>381200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>365200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>304400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>296300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>387500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>358400</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1959,90 +2138,108 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>996500</v>
+      </c>
+      <c r="E43" s="3">
+        <v>995200</v>
+      </c>
+      <c r="F43" s="3">
         <v>1091000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1028800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>922500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>987700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>1020600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1020000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>894000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>856500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>1000500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>974000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>856600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>792200</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>27100</v>
+      </c>
+      <c r="E44" s="3">
+        <v>27000</v>
+      </c>
+      <c r="F44" s="3">
         <v>27300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>25700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>23800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>25500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>23300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>23200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>21900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>21000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>22200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>21600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>20400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>18800</v>
       </c>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2082,49 +2279,61 @@
       <c r="O45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1565100</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1563200</v>
+      </c>
+      <c r="F46" s="3">
         <v>1618700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>1526500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>1451400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>1553800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1493700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1492700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1365000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1307700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1327100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>1291900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>1321500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>1222200</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2164,90 +2373,108 @@
       <c r="O47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1024100</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1022800</v>
+      </c>
+      <c r="F48" s="3">
         <v>923000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>870400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>867300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>928600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>838000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>837500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>852900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>817100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>830000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>808000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>836700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>773800</v>
       </c>
     </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2357600</v>
+      </c>
+      <c r="E49" s="3">
+        <v>2354600</v>
+      </c>
+      <c r="F49" s="3">
         <v>2156500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>2033600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>2090800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>2238400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>2173100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>2171700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>2186700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>2094900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>2163300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>2106000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>2146300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>1984900</v>
       </c>
     </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2287,8 +2514,14 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2328,49 +2561,61 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>59000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>58900</v>
+      </c>
+      <c r="F52" s="3">
         <v>38900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>36700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>43900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>47000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>27700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>27700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>37800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>36200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>32000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>31200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>35800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>33100</v>
       </c>
     </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2410,49 +2655,61 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5062600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>5056200</v>
+      </c>
+      <c r="F54" s="3">
         <v>4806000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>4532200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>4506100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>4824200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>4596200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>4593200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>4506400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>4317400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>4429000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>4311700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>4410300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>4078600</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2468,8 +2725,10 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2485,254 +2744,292 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>309200</v>
+      </c>
+      <c r="E57" s="3">
+        <v>308800</v>
+      </c>
+      <c r="F57" s="3">
         <v>945300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>891500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>279200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>298900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>882500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>881900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>260900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>249900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>866000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>843100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>207400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>191800</v>
       </c>
     </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>314800</v>
+      </c>
+      <c r="E58" s="3">
+        <v>314400</v>
+      </c>
+      <c r="F58" s="3">
         <v>170800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>161100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>214600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>229700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>147100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>147000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>213200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>204300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>469900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>457500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>401200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>371100</v>
       </c>
     </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>413500</v>
+      </c>
+      <c r="E59" s="3">
+        <v>412900</v>
+      </c>
+      <c r="F59" s="3">
         <v>95900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>90400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>421600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>451400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>147600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>147500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>387000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>370700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>94800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>92300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>397000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>367200</v>
       </c>
     </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1445900</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1444100</v>
+      </c>
+      <c r="F60" s="3">
         <v>1212100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1143000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1314600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>1407500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>1177200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1176500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1250200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1197700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>1430800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>1392900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>1377200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>1273600</v>
       </c>
     </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1903500</v>
+      </c>
+      <c r="E61" s="3">
+        <v>1901100</v>
+      </c>
+      <c r="F61" s="3">
         <v>1810900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>1707800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>1215600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>1301400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>1570000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>1569000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>1337800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>1281700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>1218900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>1186700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>1263600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>1168600</v>
       </c>
     </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>47800</v>
+      </c>
+      <c r="E62" s="3">
+        <v>47700</v>
+      </c>
+      <c r="F62" s="3">
         <v>90100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>85000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>45300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>48500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>52100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>52000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>75800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>72600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>61600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>60000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>51300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>47500</v>
       </c>
     </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2772,8 +3069,14 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2813,8 +3116,14 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2854,49 +3163,61 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3545100</v>
+      </c>
+      <c r="E66" s="3">
+        <v>3540600</v>
+      </c>
+      <c r="F66" s="3">
         <v>3202200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>3019800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>2697100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>2887500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>2886100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>2884300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>2774000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>2657600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>2821400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>2746700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>2822200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>2610000</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2912,8 +3233,10 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2953,8 +3276,14 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2994,8 +3323,14 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3035,8 +3370,14 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3076,49 +3417,61 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1450600</v>
+      </c>
+      <c r="E72" s="3">
+        <v>1448800</v>
+      </c>
+      <c r="F72" s="3">
         <v>1560500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>1471600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>1669700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>1787600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>1523600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>1522600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>1517700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>1454000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>1378000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>1341500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>1284300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>1187700</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3158,8 +3511,14 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3199,8 +3558,14 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3240,49 +3605,61 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1457500</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1455600</v>
+      </c>
+      <c r="F76" s="3">
         <v>1546100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>1458000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>1755100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>1879000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>1653800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>1652700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>1685700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>1615000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>1563100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>1521700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>1547100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>1430800</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3322,54 +3699,66 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3409,8 +3798,14 @@
       <c r="O81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3426,49 +3821,57 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>46100</v>
+      </c>
+      <c r="E83" s="3">
+        <v>49300</v>
+      </c>
+      <c r="F83" s="3">
         <v>44700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>44700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>48500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>46400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>50800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>49400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>49900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>46200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>47000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>50800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>52100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>51900</v>
       </c>
     </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3508,8 +3911,14 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3549,8 +3958,14 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3590,8 +4005,14 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3631,8 +4052,14 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3672,49 +4099,61 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>264200</v>
+      </c>
+      <c r="E89" s="3">
+        <v>263900</v>
+      </c>
+      <c r="F89" s="3">
         <v>98600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>93000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>265100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>283800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>109700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>109600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>240700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>230600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>99800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>97100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>236400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>218600</v>
       </c>
     </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3730,49 +4169,57 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-55700</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-55600</v>
+      </c>
+      <c r="F91" s="3">
         <v>-42300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-39900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-49700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-53200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-35100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-35100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-41700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-40000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-32700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-31800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-45400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-42000</v>
       </c>
     </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3812,8 +4259,14 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3853,49 +4306,61 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-151300</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-151200</v>
+      </c>
+      <c r="F94" s="3">
         <v>-45800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-43200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-46200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-49500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-43200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-43200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-51700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-49500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-40700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-39600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-82200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-76000</v>
       </c>
     </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3911,49 +4376,57 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>60000</v>
+      </c>
+      <c r="E96" s="3">
+        <v>59900</v>
+      </c>
+      <c r="F96" s="3">
         <v>111700</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>105400</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>54300</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>58200</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>75400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>75300</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>38800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>37200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>73300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>71400</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>33200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>30700</v>
       </c>
     </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3993,8 +4466,14 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4034,8 +4513,14 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4075,127 +4560,151 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-139400</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-139200</v>
+      </c>
+      <c r="F100" s="3">
         <v>-23400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-22100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-226000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-241900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-26200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-26100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-138000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-132200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-101300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-98700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-102200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-94500</v>
       </c>
     </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="F101" s="3">
         <v>-4700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-4700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-10900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-10400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-11900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-11600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-4600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-4200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>7700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>8300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>7500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-24800</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-24700</v>
+      </c>
+      <c r="F102" s="3">
         <v>17100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>16100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-11500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-12300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>35600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>35600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>40200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>38500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-54100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-52700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>47400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>43800</v>
       </c>
     </row>
